--- a/data/trans_dic/P6904-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,4; 80,84</t>
+          <t>62,52; 80,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,02; 72,06</t>
+          <t>46,01; 70,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,14; 68,88</t>
+          <t>41,76; 70,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,6; 90,7</t>
+          <t>59,81; 91,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,84; 72,49</t>
+          <t>39,82; 72,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,28; 68,78</t>
+          <t>35,58; 68,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,92; 82,69</t>
+          <t>38,88; 83,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,43; 90,85</t>
+          <t>56,47; 90,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,88; 75,8</t>
+          <t>60,34; 76,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,56; 65,78</t>
+          <t>45,72; 66,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,84; 69,71</t>
+          <t>45,53; 69,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,87; 86,13</t>
+          <t>63,45; 86,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,16; 56,12</t>
+          <t>43,6; 56,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,41; 62,95</t>
+          <t>49,14; 63,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,75; 70,05</t>
+          <t>56,89; 70,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,24; 68,59</t>
+          <t>54,8; 68,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,47; 68,39</t>
+          <t>49,9; 67,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,62; 66,87</t>
+          <t>50,08; 68,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,74; 80,96</t>
+          <t>66,51; 81,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,61; 82,33</t>
+          <t>62,11; 79,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,86; 57,58</t>
+          <t>47,49; 57,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,77; 63,15</t>
+          <t>52,14; 62,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62,41; 72,77</t>
+          <t>62,01; 72,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,95; 73,12</t>
+          <t>60,64; 73,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 43,36</t>
+          <t>20,94; 41,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,68; 56,17</t>
+          <t>25,81; 56,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 62,16</t>
+          <t>36,36; 62,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,07; 66,28</t>
+          <t>39,1; 66,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,58; 49,07</t>
+          <t>24,85; 49,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 48,9</t>
+          <t>17,29; 46,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,99; 67,89</t>
+          <t>44,73; 68,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,18; 60,49</t>
+          <t>42,25; 60,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,14; 42,52</t>
+          <t>25,57; 42,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,99; 46,84</t>
+          <t>25,61; 46,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,58; 61,52</t>
+          <t>44,03; 61,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,02; 58,84</t>
+          <t>45,04; 60,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,36; 56,78</t>
+          <t>47,09; 56,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,1; 60,44</t>
+          <t>48,78; 60,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,86; 64,86</t>
+          <t>53,82; 64,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,25; 66,77</t>
+          <t>55,7; 66,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,5; 59,0</t>
+          <t>44,96; 58,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,37; 58,36</t>
+          <t>44,95; 58,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,83; 73,65</t>
+          <t>60,93; 73,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,42; 74,34</t>
+          <t>59,39; 74,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,19; 55,86</t>
+          <t>48,28; 55,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,11; 57,71</t>
+          <t>49,08; 57,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,68; 66,38</t>
+          <t>58,3; 66,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,2; 69,48</t>
+          <t>59,25; 69,25</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70558; 89969</t>
+          <t>69578; 89493</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27133; 41580</t>
+          <t>26549; 40906</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23422; 38282</t>
+          <t>23212; 39253</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17119; 26498</t>
+          <t>17472; 26601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14592; 27232</t>
+          <t>14959; 27062</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13764; 26093</t>
+          <t>13496; 26093</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7016; 14904</t>
+          <t>7007; 14967</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13848; 22700</t>
+          <t>14109; 22533</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89138; 112833</t>
+          <t>89819; 113474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43575; 62907</t>
+          <t>43723; 63562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33005; 51312</t>
+          <t>33513; 50867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34074; 46684</t>
+          <t>34387; 47096</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126718; 161042</t>
+          <t>125114; 161134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>109053; 138929</t>
+          <t>108453; 139592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130172; 160683</t>
+          <t>130490; 161344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132341; 164322</t>
+          <t>131290; 164124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58656; 81089</t>
+          <t>59169; 79731</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64768; 87285</t>
+          <t>65363; 88860</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81892; 100846</t>
+          <t>82844; 101658</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>149239; 196259</t>
+          <t>148050; 190573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194089; 233513</t>
+          <t>192566; 233895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181839; 221808</t>
+          <t>183125; 219773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220911; 257563</t>
+          <t>219484; 255203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>291300; 349489</t>
+          <t>289841; 350350</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15418; 32121</t>
+          <t>15510; 31006</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12296; 25887</t>
+          <t>11895; 26179</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22699; 39491</t>
+          <t>23097; 39493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27859; 46080</t>
+          <t>27185; 45954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15728; 31396</t>
+          <t>15898; 31350</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8347; 22102</t>
+          <t>7812; 21129</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32424; 50041</t>
+          <t>32969; 50738</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36440; 54864</t>
+          <t>38320; 55068</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36083; 58697</t>
+          <t>35296; 58507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23726; 42757</t>
+          <t>23381; 42490</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59805; 84431</t>
+          <t>60428; 84108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70527; 94280</t>
+          <t>72157; 96719</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223693; 268198</t>
+          <t>222390; 267606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159330; 196140</t>
+          <t>158291; 196569</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187710; 226036</t>
+          <t>187557; 226433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>186934; 225889</t>
+          <t>188451; 226652</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100160; 129872</t>
+          <t>98975; 128347</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94801; 124703</t>
+          <t>96046; 125458</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131567; 159313</t>
+          <t>131790; 158949</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>210361; 263187</t>
+          <t>210286; 264360</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>333659; 386773</t>
+          <t>334291; 387206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>264294; 310550</t>
+          <t>264105; 310470</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>325792; 374931</t>
+          <t>329246; 374833</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>409856; 481090</t>
+          <t>410245; 479483</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6904-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,52; 80,42</t>
+          <t>63,16; 80,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,01; 70,89</t>
+          <t>45,33; 70,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,76; 70,62</t>
+          <t>42,7; 68,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,81; 91,05</t>
+          <t>63,6; 91,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,82; 72,04</t>
+          <t>39,99; 72,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,58; 68,78</t>
+          <t>35,29; 67,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,88; 83,04</t>
+          <t>39,17; 80,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,47; 90,18</t>
+          <t>51,07; 83,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,34; 76,23</t>
+          <t>60,34; 75,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,72; 66,46</t>
+          <t>44,46; 65,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,53; 69,11</t>
+          <t>44,5; 68,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,45; 86,89</t>
+          <t>64,19; 84,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,6; 56,15</t>
+          <t>43,76; 55,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,14; 63,25</t>
+          <t>49,16; 63,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,89; 70,34</t>
+          <t>56,1; 70,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,8; 68,5</t>
+          <t>57,59; 69,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,9; 67,24</t>
+          <t>49,69; 67,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,08; 68,08</t>
+          <t>49,54; 67,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,51; 81,61</t>
+          <t>66,57; 80,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,11; 79,95</t>
+          <t>58,35; 69,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,49; 57,68</t>
+          <t>47,34; 57,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,14; 62,57</t>
+          <t>51,74; 62,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62,01; 72,1</t>
+          <t>62,65; 72,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,64; 73,3</t>
+          <t>59,78; 68,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 41,86</t>
+          <t>20,46; 42,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,81; 56,8</t>
+          <t>26,44; 56,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 62,17</t>
+          <t>35,49; 61,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 66,1</t>
+          <t>37,65; 63,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 49,0</t>
+          <t>23,97; 49,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,29; 46,75</t>
+          <t>17,05; 46,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,73; 68,84</t>
+          <t>44,53; 67,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,25; 60,72</t>
+          <t>42,13; 60,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,57; 42,38</t>
+          <t>25,43; 42,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,61; 46,55</t>
+          <t>26,77; 48,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,03; 61,29</t>
+          <t>43,09; 61,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,04; 60,37</t>
+          <t>44,45; 60,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,09; 56,66</t>
+          <t>47,51; 57,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,78; 60,58</t>
+          <t>48,65; 60,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,82; 64,98</t>
+          <t>53,7; 64,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,7; 66,99</t>
+          <t>57,59; 68,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,31</t>
+          <t>44,66; 58,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,72</t>
+          <t>44,7; 58,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,93; 73,49</t>
+          <t>60,78; 73,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,39; 74,67</t>
+          <t>55,83; 65,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,28; 55,92</t>
+          <t>48,48; 56,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,69</t>
+          <t>48,92; 58,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,3; 66,37</t>
+          <t>58,07; 66,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,25; 69,25</t>
+          <t>58,44; 65,69</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>45868</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69578; 89493</t>
+          <t>70291; 89910</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26549; 40906</t>
+          <t>26158; 40537</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23212; 39253</t>
+          <t>23735; 38236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17472; 26601</t>
+          <t>23032; 33150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14959; 27062</t>
+          <t>15024; 27127</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13496; 26093</t>
+          <t>13385; 25589</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7007; 14967</t>
+          <t>7060; 14463</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14109; 22533</t>
+          <t>12515; 20451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89819; 113474</t>
+          <t>89819; 113001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43723; 63562</t>
+          <t>42521; 62678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33513; 50867</t>
+          <t>32751; 50671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34387; 47096</t>
+          <t>38978; 51334</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148652</t>
+          <t>173513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>166222</t>
+          <t>142152</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>314874</t>
+          <t>315665</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125114; 161134</t>
+          <t>125575; 159194</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>108453; 139592</t>
+          <t>108500; 139066</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130490; 161344</t>
+          <t>128691; 161111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131290; 164124</t>
+          <t>155334; 188698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59169; 79731</t>
+          <t>58916; 79473</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65363; 88860</t>
+          <t>64661; 88576</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82844; 101658</t>
+          <t>82927; 100512</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>148050; 190573</t>
+          <t>128869; 154006</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>192566; 233895</t>
+          <t>191963; 234120</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>183125; 219773</t>
+          <t>181744; 220582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>219484; 255203</t>
+          <t>221739; 255839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>289841; 350350</t>
+          <t>293258; 336022</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>39736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46314</t>
+          <t>51484</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82876</t>
+          <t>91220</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15510; 31006</t>
+          <t>15155; 31335</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11895; 26179</t>
+          <t>12187; 25894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23097; 39493</t>
+          <t>22548; 39326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27185; 45954</t>
+          <t>29279; 49199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15898; 31350</t>
+          <t>15334; 31660</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7812; 21129</t>
+          <t>7706; 21079</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32969; 50738</t>
+          <t>32820; 49860</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38320; 55068</t>
+          <t>41884; 60132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35296; 58507</t>
+          <t>35115; 57988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23381; 42490</t>
+          <t>24433; 43988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60428; 84108</t>
+          <t>59137; 84174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72157; 96719</t>
+          <t>78761; 106910</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207589</t>
+          <t>242263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>231260</t>
+          <t>210491</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>438849</t>
+          <t>452754</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>222390; 267606</t>
+          <t>224382; 270196</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>158291; 196569</t>
+          <t>157869; 197058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187557; 226433</t>
+          <t>187145; 225844</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>188451; 226652</t>
+          <t>220978; 261979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>98975; 128347</t>
+          <t>98303; 128383</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96046; 125458</t>
+          <t>95508; 124256</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131790; 158949</t>
+          <t>131465; 158442</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>210286; 264360</t>
+          <t>192496; 225120</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>334291; 387206</t>
+          <t>335689; 388595</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>264105; 310470</t>
+          <t>263260; 313126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>329246; 374833</t>
+          <t>327965; 376613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>410245; 479483</t>
+          <t>425754; 478551</t>
         </is>
       </c>
     </row>
